--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-21 19:37:35</t>
+          <t>2026-08-22 00:38:47</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-22 00:38:47</t>
+          <t>2026-08-22 11:12:30</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,35 +454,50 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Property_Type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Statutory_Deadline_Window</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Clerk_Verification_URL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -522,35 +537,50 @@
           <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>128500</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>32125</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>TX Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -588,35 +618,50 @@
           <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>86200</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>21550</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>TX Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -654,35 +699,50 @@
           <t>6412 ABRAMS RD DALLAS TX 75231</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>77800</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>19450</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://www.dallascounty.org/</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>TX Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -720,35 +780,50 @@
           <t>3819 COLONIAL AVE DALLAS TX 75215</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>59400</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>14850</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://www.dallascounty.org/</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>TX Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>
@@ -786,35 +861,50 @@
           <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Commercial / Mixed Use</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>41300</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>10325</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>TX Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-08-22 11:12:30</t>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:56:15</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-23 12:56:15</t>
+          <t>2026-08-24 13:47:38</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:47:38</t>
+          <t>2026-08-24 15:33:23</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:33:23</t>
+          <t>2026-08-25 11:18:14</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,55 +449,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Heir_Search_Recommended</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -532,55 +537,58 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>128500</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>32125</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -613,55 +621,58 @@
       <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Commercial / Mixed Use</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>86200</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>21550</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -694,55 +705,58 @@
       <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>6412 ABRAMS RD DALLAS TX 75231</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>77800</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>19450</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>TX Tax Code § 34.04</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -775,55 +789,58 @@
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>3819 COLONIAL AVE DALLAS TX 75215</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>59400</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>14850</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>TX Tax Code § 34.04</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>
@@ -856,55 +873,58 @@
       <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Commercial / Mixed Use</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>41300</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>10325</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2 Years from Sale (TX Tax Code § 34.04)</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>TX Tax Code § 34.04</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:14</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:41:32</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,20 +489,30 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Days_Remaining_To_Claim</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Claim_Urgency_Tier</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -571,24 +581,32 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>671</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -655,24 +673,32 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>678</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -739,24 +765,32 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>706</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -823,24 +857,32 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>685</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -907,24 +949,32 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>699</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>

--- a/exports/Texas_Surplus_Feed.xlsx
+++ b/exports/Texas_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:39</t>
         </is>
       </c>
     </row>
